--- a/01_Data/03_Test_Cases/caso_COL18_E0_24h.xlsx
+++ b/01_Data/03_Test_Cases/caso_COL18_E0_24h.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\My Drive\2. Universidad Nacional de Colombia\2. Postgraduate\1_SEMESTER\TESIS DE MAESTRIA\2nd Search\04_TESIS_DANIEL\03_CODIGO_TRABAJO_DANIEL\BESS_FACTS_master\01_Data\03_Test_Cases\Colombian system\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\My Drive\2. Universidad Nacional de Colombia\2. Postgraduate\1_SEMESTER\TESIS DE MAESTRIA\2nd Search\04_TESIS_DANIEL\03_CODIGO_TRABAJO_DANIEL\BESS_FACTS_master\01_Data\03_Test_Cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58AEECCF-9873-4964-9A71-2AE9B4AED43B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INSTRUCCIONES" sheetId="1" r:id="rId1"/>
